--- a/Gantt_Proyecto_Integrador_IDGS10A_2026_Equipo4_Donaton.xlsx
+++ b/Gantt_Proyecto_Integrador_IDGS10A_2026_Equipo4_Donaton.xlsx
@@ -484,19 +484,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -516,23 +516,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -552,51 +552,51 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -604,7 +604,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1065,7 +1065,7 @@
       <c r="M8" s="9"/>
       <c r="P8" s="14" t="n">
         <f aca="false">AVERAGE(E5,E6,F7,F8,F9,G10,G11,G12,K13,K14,M15)</f>
-        <v>0.636363636363636</v>
+        <v>0.854545454545455</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
@@ -1162,7 +1162,7 @@
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="17" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H12" s="17"/>
       <c r="I12" s="17"/>
@@ -1191,7 +1191,7 @@
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
       <c r="K13" s="17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L13" s="17"/>
       <c r="M13" s="9"/>
@@ -1216,7 +1216,7 @@
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
       <c r="K14" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="17"/>
       <c r="M14" s="9"/>

--- a/Gantt_Proyecto_Integrador_IDGS10A_2026_Equipo4_Donaton.xlsx
+++ b/Gantt_Proyecto_Integrador_IDGS10A_2026_Equipo4_Donaton.xlsx
@@ -115,7 +115,7 @@
     <t xml:space="preserve">Liberación a PRD</t>
   </si>
   <si>
-    <t xml:space="preserve">8</t>
+    <t xml:space="preserve">Actualizaciones de revisión</t>
   </si>
   <si>
     <t xml:space="preserve">Presentación Final</t>
@@ -864,11 +864,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr defaultColWidth="8.859375" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="35.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="14.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="7.71"/>
@@ -1064,8 +1064,8 @@
       <c r="L8" s="9"/>
       <c r="M8" s="9"/>
       <c r="P8" s="14" t="n">
-        <f aca="false">AVERAGE(E5,E6,F7,F8,F9,G10,G11,G12,K13,K14,M15)</f>
-        <v>0.854545454545455</v>
+        <f aca="false">AVERAGE(E5,E6,F7,F8,F9,G10,G11,G12,K13,K14,K15,M16)</f>
+        <v>0.8</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
@@ -1221,18 +1221,18 @@
       <c r="L14" s="17"/>
       <c r="M14" s="9"/>
     </row>
-    <row r="15" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>31</v>
+      <c r="C15" s="20" t="n">
+        <v>46218</v>
+      </c>
+      <c r="D15" s="20" t="n">
+        <v>46223</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
@@ -1240,144 +1240,169 @@
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="17" t="n">
+      <c r="K15" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L15" s="17"/>
+      <c r="M15" s="9"/>
+    </row>
+    <row r="16" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="17" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="22" t="s">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="21"/>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-    </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="23"/>
+      <c r="B19" s="24" t="s">
         <v>33</v>
-      </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-    </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="25"/>
-      <c r="B19" s="24" t="s">
-        <v>34</v>
       </c>
       <c r="C19" s="24"/>
       <c r="D19" s="24"/>
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
     </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="26"/>
-      <c r="B20" s="1" t="s">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="25"/>
+      <c r="B20" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="26"/>
+      <c r="B21" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="27" t="s">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="27"/>
-      <c r="M22" s="27"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="28" t="s">
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="28"/>
       <c r="B24" s="28"/>
       <c r="C24" s="28"/>
       <c r="D24" s="28"/>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="28" t="s">
-        <v>38</v>
-      </c>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="28"/>
       <c r="B25" s="28"/>
       <c r="C25" s="28"/>
       <c r="D25" s="28"/>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="28"/>
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="28" t="s">
+        <v>38</v>
+      </c>
       <c r="B26" s="28"/>
       <c r="C26" s="28"/>
       <c r="D26" s="28"/>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="29" t="s">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="28"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+    </row>
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="29"/>
-      <c r="M28" s="29"/>
-    </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="30" t="s">
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-    </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="31"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+    </row>
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="31"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="F7:G7"/>
@@ -1390,17 +1415,18 @@
     <mergeCell ref="G12:J12"/>
     <mergeCell ref="K13:L13"/>
     <mergeCell ref="K14:L14"/>
-    <mergeCell ref="A17:M17"/>
-    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="A18:M18"/>
     <mergeCell ref="B19:F19"/>
-    <mergeCell ref="A22:M22"/>
-    <mergeCell ref="A23:D24"/>
-    <mergeCell ref="A25:D26"/>
-    <mergeCell ref="A28:M28"/>
-    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="A23:M23"/>
+    <mergeCell ref="A24:D25"/>
+    <mergeCell ref="A26:D27"/>
+    <mergeCell ref="A29:M29"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A29" r:id="rId1" display="www.github.com/AdrianFMz/Donaton_3.0"/>
+    <hyperlink ref="A30" r:id="rId1" display="www.github.com/AdrianFMz/Donaton_3.0"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
